--- a/output/2026-10-03_17_Malesia_Perak_Cleaning.xlsx
+++ b/output/2026-10-03_17_Malesia_Perak_Cleaning.xlsx
@@ -474,7 +474,6 @@
           <t>Wah Seng Sin Kee Co Sdn Bhd (WSSK)</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Ipoh, Perak (TBK 365, Jalan Menglembu, 31450 Ipoh)</t>
@@ -485,8 +484,6 @@
           <t>Hardware/ferramenta generale - possibile gamma attrezzature pulizia NON confermata specificamente</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Azienda storica (attiva dai primi anni '50) di hardware trading con sede a Ipoh e filiali a Kuala Lumpur, Kuantan e Butterworth. Esistenza confermata via jobstore.my. Nessuna conferma diretta che tratti specificamente attrezzature/prodotti per pulizia industriale (settore dichiarato: hardware generale) - necessaria verifica umana diretta (es. telefonata o visita) per confermare la gamma prodotti e ottenere contatti telefono/email.</t>
@@ -524,7 +521,6 @@
           <t>1300 88 2388 / +603-5614 8303</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Filiale locale reale e verificata in Perak (Ipoh/Chemor) del gruppo Rentokil Initial. Modello commerciale basato su noleggio/contratto di servizio igiene, non vendita diretta di macchine industriali: verificare con l'azienda se il profilo rientra nella definizione di 'distributore' richiesta per questo progetto o va trattato come fornitore di servizi. Email generica non reperita.</t>
@@ -532,7 +528,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
